--- a/artifacts/exports/shuori-demo-workspace.xlsx
+++ b/artifacts/exports/shuori-demo-workspace.xlsx
@@ -84,12 +84,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2756" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2756" uniqueCount="638">
   <si>
     <t>守織 SHUORI · Workbook overview</t>
   </si>
   <si>
-    <t>Generated 2026-10-08 17:07:05 JST · Asia/Tokyo · demo · version 1.3.0</t>
+    <t>Generated 2026-10-08 17:31:54 JST · Asia/Tokyo · demo · version 1.3.0</t>
   </si>
   <si>
     <t>workspace | All records in the stated scope | View label: All saved operational collections</t>
@@ -631,7 +631,7 @@
     <t>Stories that connect</t>
   </si>
   <si>
-    <t>Support Nikoniko Bunko Plus with a welcoming reading programme and a refreshed circulation workflow.</t>
+    <t>Support the library with a welcoming reading programme and a refreshed circulation workflow.</t>
   </si>
   <si>
     <t>Library team</t>
@@ -982,7 +982,7 @@
     <t>library</t>
   </si>
   <si>
-    <t>Nikoniko Bunko Plus</t>
+    <t>Library</t>
   </si>
   <si>
     <t>6F</t>
@@ -1941,10 +1941,7 @@
     <t>Central Clinical Building 2</t>
   </si>
   <si>
-    <t>official</t>
-  </si>
-  <si>
-    <t>Official library building and floor. Open Monday, Wednesday and Friday, 10:00–14:30. Geometry, station coordinates and capacity are illustrative.</t>
+    <t>Illustrative library station in the demonstration model. Names, coordinates and capacity are examples; confirm the local library location and opening hours before scheduling.</t>
   </si>
   <si>
     <t>garden</t>
@@ -3020,10 +3017,10 @@
         <v>1</v>
       </c>
       <c r="M6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="N6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3064,10 +3061,10 @@
         <v>1</v>
       </c>
       <c r="M7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="N7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3108,10 +3105,10 @@
         <v>1</v>
       </c>
       <c r="M8" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="N8" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3152,10 +3149,10 @@
         <v>1</v>
       </c>
       <c r="M9" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="N9" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3196,10 +3193,10 @@
         <v>1</v>
       </c>
       <c r="M10" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="N10" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
   </sheetData>
@@ -3906,10 +3903,10 @@
         <v>1</v>
       </c>
       <c r="H6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="I6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3935,10 +3932,10 @@
         <v>1</v>
       </c>
       <c r="H7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="I7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3964,10 +3961,10 @@
         <v>1</v>
       </c>
       <c r="H8" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="I8" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3993,10 +3990,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="I9" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
   </sheetData>
@@ -4317,10 +4314,10 @@
         <v>1</v>
       </c>
       <c r="Y6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="Z6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
@@ -4391,10 +4388,10 @@
         <v>1</v>
       </c>
       <c r="Y7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="Z7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
@@ -4463,10 +4460,10 @@
         <v>1</v>
       </c>
       <c r="Y8" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="Z8" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
   </sheetData>
@@ -5137,10 +5134,10 @@
         <v>1</v>
       </c>
       <c r="AA6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="AB6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="7" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5211,10 +5208,10 @@
         <v>1</v>
       </c>
       <c r="AA7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="AB7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="8" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5285,10 +5282,10 @@
         <v>1</v>
       </c>
       <c r="AA8" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="AB8" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="9" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5357,10 +5354,10 @@
         <v>1</v>
       </c>
       <c r="AA9" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="AB9" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="10" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5429,10 +5426,10 @@
         <v>1</v>
       </c>
       <c r="AA10" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="AB10" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="11" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5501,10 +5498,10 @@
         <v>1</v>
       </c>
       <c r="AA11" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="AB11" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="12" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5573,10 +5570,10 @@
         <v>1</v>
       </c>
       <c r="AA12" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="AB12" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="13" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5645,10 +5642,10 @@
         <v>1</v>
       </c>
       <c r="AA13" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="AB13" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="14" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5717,10 +5714,10 @@
         <v>1</v>
       </c>
       <c r="AA14" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="AB14" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="15" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5789,10 +5786,10 @@
         <v>1</v>
       </c>
       <c r="AA15" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="AB15" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="16" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5861,10 +5858,10 @@
         <v>1</v>
       </c>
       <c r="AA16" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="AB16" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="17" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5933,10 +5930,10 @@
         <v>1</v>
       </c>
       <c r="AA17" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="AB17" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="18" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -6005,10 +6002,10 @@
         <v>1</v>
       </c>
       <c r="AA18" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="AB18" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="19" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -6077,10 +6074,10 @@
         <v>1</v>
       </c>
       <c r="AA19" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="AB19" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="20" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -6151,10 +6148,10 @@
         <v>1</v>
       </c>
       <c r="AA20" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="AB20" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="21" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -6225,10 +6222,10 @@
         <v>1</v>
       </c>
       <c r="AA21" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="AB21" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="22" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -6297,10 +6294,10 @@
         <v>1</v>
       </c>
       <c r="AA22" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="AB22" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="23" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -6369,10 +6366,10 @@
         <v>1</v>
       </c>
       <c r="AA23" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="AB23" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
   </sheetData>
@@ -6870,10 +6867,10 @@
         <v>1</v>
       </c>
       <c r="N6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6909,10 +6906,10 @@
         <v>1</v>
       </c>
       <c r="N7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
   </sheetData>
@@ -7314,24 +7311,24 @@
         <v>3</v>
       </c>
       <c r="H9" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>610</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>612</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>613</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>276</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E10" s="11">
         <v>10</v>
@@ -7346,7 +7343,7 @@
         <v>605</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -7360,7 +7357,7 @@
         <v>276</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E11" s="16">
         <v>-9</v>
@@ -7375,7 +7372,7 @@
         <v>605</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -7418,7 +7415,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7485,28 +7482,28 @@
         <v>47</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>622</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>623</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>508</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>624</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>625</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>72</v>
@@ -7520,19 +7517,19 @@
     </row>
     <row r="6" ht="56" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>568</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>627</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>628</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>629</v>
       </c>
       <c r="F6" s="9" t="b">
         <v>0</v>
@@ -7544,30 +7541,30 @@
         <v>0</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="J6" s="5">
         <v>1</v>
       </c>
       <c r="K6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="L6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
+        <v>630</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>631</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="C7" s="6" t="s">
         <v>632</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="6" t="s">
         <v>633</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>634</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="14" t="b">
@@ -7580,30 +7577,30 @@
         <v>0</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="J7" s="7">
         <v>1</v>
       </c>
       <c r="K7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="L7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>635</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>636</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>637</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>638</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="9" t="b">
@@ -7616,16 +7613,16 @@
         <v>0</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="J8" s="5">
         <v>1</v>
       </c>
       <c r="K8" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="L8" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
   </sheetData>
@@ -7851,10 +7848,10 @@
         <v>1</v>
       </c>
       <c r="P6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="Q6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7904,10 +7901,10 @@
         <v>1</v>
       </c>
       <c r="P7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="Q7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7957,10 +7954,10 @@
         <v>1</v>
       </c>
       <c r="P8" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="Q8" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8010,10 +8007,10 @@
         <v>1</v>
       </c>
       <c r="P9" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="Q9" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
   </sheetData>
@@ -8256,10 +8253,10 @@
         <v>1</v>
       </c>
       <c r="R6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="S6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8315,10 +8312,10 @@
         <v>1</v>
       </c>
       <c r="R7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="S7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8374,10 +8371,10 @@
         <v>1</v>
       </c>
       <c r="R8" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="S8" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8433,10 +8430,10 @@
         <v>1</v>
       </c>
       <c r="R9" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="S9" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8492,10 +8489,10 @@
         <v>1</v>
       </c>
       <c r="R10" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="S10" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8551,10 +8548,10 @@
         <v>1</v>
       </c>
       <c r="R11" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="S11" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8606,10 +8603,10 @@
         <v>1</v>
       </c>
       <c r="R12" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="S12" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8665,10 +8662,10 @@
         <v>1</v>
       </c>
       <c r="R13" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="S13" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8724,10 +8721,10 @@
         <v>1</v>
       </c>
       <c r="R14" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="S14" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8783,10 +8780,10 @@
         <v>1</v>
       </c>
       <c r="R15" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="S15" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8838,10 +8835,10 @@
         <v>1</v>
       </c>
       <c r="R16" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="S16" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8893,10 +8890,10 @@
         <v>1</v>
       </c>
       <c r="R17" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="S17" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8952,10 +8949,10 @@
         <v>1</v>
       </c>
       <c r="R18" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="S18" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9011,10 +9008,10 @@
         <v>1</v>
       </c>
       <c r="R19" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="S19" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9066,10 +9063,10 @@
         <v>1</v>
       </c>
       <c r="R20" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="S20" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9125,10 +9122,10 @@
         <v>1</v>
       </c>
       <c r="R21" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="S21" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9184,10 +9181,10 @@
         <v>1</v>
       </c>
       <c r="R22" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="S22" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9243,10 +9240,10 @@
         <v>1</v>
       </c>
       <c r="R23" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="S23" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
   </sheetData>
@@ -9810,10 +9807,10 @@
         <v>1</v>
       </c>
       <c r="S6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -9872,10 +9869,10 @@
         <v>1</v>
       </c>
       <c r="S7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -9934,10 +9931,10 @@
         <v>1</v>
       </c>
       <c r="S8" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T8" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -9996,10 +9993,10 @@
         <v>1</v>
       </c>
       <c r="S9" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T9" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10058,10 +10055,10 @@
         <v>1</v>
       </c>
       <c r="S10" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T10" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10120,10 +10117,10 @@
         <v>1</v>
       </c>
       <c r="S11" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T11" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10182,10 +10179,10 @@
         <v>1</v>
       </c>
       <c r="S12" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T12" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10244,10 +10241,10 @@
         <v>1</v>
       </c>
       <c r="S13" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T13" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10306,10 +10303,10 @@
         <v>1</v>
       </c>
       <c r="S14" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T14" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10368,10 +10365,10 @@
         <v>1</v>
       </c>
       <c r="S15" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T15" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10430,10 +10427,10 @@
         <v>1</v>
       </c>
       <c r="S16" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T16" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10492,10 +10489,10 @@
         <v>1</v>
       </c>
       <c r="S17" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T17" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10554,10 +10551,10 @@
         <v>1</v>
       </c>
       <c r="S18" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T18" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10616,10 +10613,10 @@
         <v>1</v>
       </c>
       <c r="S19" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T19" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10678,10 +10675,10 @@
         <v>1</v>
       </c>
       <c r="S20" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T20" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10740,10 +10737,10 @@
         <v>1</v>
       </c>
       <c r="S21" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T21" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10802,10 +10799,10 @@
         <v>1</v>
       </c>
       <c r="S22" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T22" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10864,10 +10861,10 @@
         <v>1</v>
       </c>
       <c r="S23" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T23" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10926,10 +10923,10 @@
         <v>1</v>
       </c>
       <c r="S24" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T24" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10988,10 +10985,10 @@
         <v>1</v>
       </c>
       <c r="S25" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T25" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11050,10 +11047,10 @@
         <v>1</v>
       </c>
       <c r="S26" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T26" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11112,10 +11109,10 @@
         <v>1</v>
       </c>
       <c r="S27" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T27" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11174,10 +11171,10 @@
         <v>1</v>
       </c>
       <c r="S28" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T28" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11236,10 +11233,10 @@
         <v>1</v>
       </c>
       <c r="S29" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T29" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11298,10 +11295,10 @@
         <v>1</v>
       </c>
       <c r="S30" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T30" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11360,10 +11357,10 @@
         <v>1</v>
       </c>
       <c r="S31" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T31" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11422,10 +11419,10 @@
         <v>1</v>
       </c>
       <c r="S32" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T32" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11484,10 +11481,10 @@
         <v>1</v>
       </c>
       <c r="S33" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T33" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11546,10 +11543,10 @@
         <v>1</v>
       </c>
       <c r="S34" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T34" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11608,10 +11605,10 @@
         <v>1</v>
       </c>
       <c r="S35" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T35" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11670,10 +11667,10 @@
         <v>1</v>
       </c>
       <c r="S36" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T36" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11732,10 +11729,10 @@
         <v>1</v>
       </c>
       <c r="S37" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T37" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11794,10 +11791,10 @@
         <v>1</v>
       </c>
       <c r="S38" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T38" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11856,10 +11853,10 @@
         <v>1</v>
       </c>
       <c r="S39" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T39" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11918,10 +11915,10 @@
         <v>1</v>
       </c>
       <c r="S40" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T40" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11980,10 +11977,10 @@
         <v>1</v>
       </c>
       <c r="S41" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T41" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12042,10 +12039,10 @@
         <v>1</v>
       </c>
       <c r="S42" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T42" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12104,10 +12101,10 @@
         <v>1</v>
       </c>
       <c r="S43" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T43" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12166,10 +12163,10 @@
         <v>1</v>
       </c>
       <c r="S44" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T44" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12228,10 +12225,10 @@
         <v>1</v>
       </c>
       <c r="S45" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T45" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12290,10 +12287,10 @@
         <v>1</v>
       </c>
       <c r="S46" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T46" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12352,10 +12349,10 @@
         <v>1</v>
       </c>
       <c r="S47" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T47" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12414,10 +12411,10 @@
         <v>1</v>
       </c>
       <c r="S48" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T48" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12476,10 +12473,10 @@
         <v>1</v>
       </c>
       <c r="S49" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T49" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12538,10 +12535,10 @@
         <v>1</v>
       </c>
       <c r="S50" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T50" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12600,10 +12597,10 @@
         <v>1</v>
       </c>
       <c r="S51" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T51" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12662,10 +12659,10 @@
         <v>1</v>
       </c>
       <c r="S52" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="T52" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
   </sheetData>
@@ -15966,10 +15963,10 @@
         <v>1</v>
       </c>
       <c r="N6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16009,10 +16006,10 @@
         <v>1</v>
       </c>
       <c r="N7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16052,10 +16049,10 @@
         <v>1</v>
       </c>
       <c r="N8" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O8" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16095,10 +16092,10 @@
         <v>1</v>
       </c>
       <c r="N9" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O9" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16138,10 +16135,10 @@
         <v>1</v>
       </c>
       <c r="N10" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O10" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16181,10 +16178,10 @@
         <v>1</v>
       </c>
       <c r="N11" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O11" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16224,10 +16221,10 @@
         <v>1</v>
       </c>
       <c r="N12" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O12" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16267,10 +16264,10 @@
         <v>1</v>
       </c>
       <c r="N13" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O13" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16310,10 +16307,10 @@
         <v>1</v>
       </c>
       <c r="N14" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O14" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16353,10 +16350,10 @@
         <v>1</v>
       </c>
       <c r="N15" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O15" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16396,10 +16393,10 @@
         <v>1</v>
       </c>
       <c r="N16" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O16" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16439,10 +16436,10 @@
         <v>1</v>
       </c>
       <c r="N17" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O17" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16482,10 +16479,10 @@
         <v>1</v>
       </c>
       <c r="N18" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O18" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16525,10 +16522,10 @@
         <v>1</v>
       </c>
       <c r="N19" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O19" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16568,10 +16565,10 @@
         <v>1</v>
       </c>
       <c r="N20" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O20" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16611,10 +16608,10 @@
         <v>1</v>
       </c>
       <c r="N21" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O21" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16654,10 +16651,10 @@
         <v>1</v>
       </c>
       <c r="N22" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O22" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16697,10 +16694,10 @@
         <v>1</v>
       </c>
       <c r="N23" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O23" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16740,10 +16737,10 @@
         <v>1</v>
       </c>
       <c r="N24" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O24" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16783,10 +16780,10 @@
         <v>1</v>
       </c>
       <c r="N25" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O25" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16826,10 +16823,10 @@
         <v>1</v>
       </c>
       <c r="N26" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O26" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16869,10 +16866,10 @@
         <v>1</v>
       </c>
       <c r="N27" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O27" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16912,10 +16909,10 @@
         <v>1</v>
       </c>
       <c r="N28" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O28" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16955,10 +16952,10 @@
         <v>1</v>
       </c>
       <c r="N29" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O29" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16998,10 +16995,10 @@
         <v>1</v>
       </c>
       <c r="N30" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O30" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17041,10 +17038,10 @@
         <v>1</v>
       </c>
       <c r="N31" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O31" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17084,10 +17081,10 @@
         <v>1</v>
       </c>
       <c r="N32" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O32" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17127,10 +17124,10 @@
         <v>1</v>
       </c>
       <c r="N33" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O33" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17170,10 +17167,10 @@
         <v>1</v>
       </c>
       <c r="N34" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O34" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17213,10 +17210,10 @@
         <v>1</v>
       </c>
       <c r="N35" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O35" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17256,10 +17253,10 @@
         <v>1</v>
       </c>
       <c r="N36" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O36" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17299,10 +17296,10 @@
         <v>1</v>
       </c>
       <c r="N37" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O37" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17342,10 +17339,10 @@
         <v>1</v>
       </c>
       <c r="N38" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O38" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17385,10 +17382,10 @@
         <v>1</v>
       </c>
       <c r="N39" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O39" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17428,10 +17425,10 @@
         <v>1</v>
       </c>
       <c r="N40" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O40" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17471,10 +17468,10 @@
         <v>1</v>
       </c>
       <c r="N41" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O41" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17514,10 +17511,10 @@
         <v>1</v>
       </c>
       <c r="N42" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O42" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17557,10 +17554,10 @@
         <v>1</v>
       </c>
       <c r="N43" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O43" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17600,10 +17597,10 @@
         <v>1</v>
       </c>
       <c r="N44" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O44" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17643,10 +17640,10 @@
         <v>1</v>
       </c>
       <c r="N45" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O45" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17686,10 +17683,10 @@
         <v>1</v>
       </c>
       <c r="N46" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O46" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17729,10 +17726,10 @@
         <v>1</v>
       </c>
       <c r="N47" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O47" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17772,10 +17769,10 @@
         <v>1</v>
       </c>
       <c r="N48" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O48" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17815,10 +17812,10 @@
         <v>1</v>
       </c>
       <c r="N49" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O49" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17858,10 +17855,10 @@
         <v>1</v>
       </c>
       <c r="N50" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O50" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17901,10 +17898,10 @@
         <v>1</v>
       </c>
       <c r="N51" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O51" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17944,10 +17941,10 @@
         <v>1</v>
       </c>
       <c r="N52" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O52" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17987,10 +17984,10 @@
         <v>1</v>
       </c>
       <c r="N53" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O53" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18030,10 +18027,10 @@
         <v>1</v>
       </c>
       <c r="N54" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O54" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18073,10 +18070,10 @@
         <v>1</v>
       </c>
       <c r="N55" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O55" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18116,10 +18113,10 @@
         <v>1</v>
       </c>
       <c r="N56" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O56" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18159,10 +18156,10 @@
         <v>1</v>
       </c>
       <c r="N57" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O57" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18202,10 +18199,10 @@
         <v>1</v>
       </c>
       <c r="N58" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O58" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18245,10 +18242,10 @@
         <v>1</v>
       </c>
       <c r="N59" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O59" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="60" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18288,10 +18285,10 @@
         <v>1</v>
       </c>
       <c r="N60" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O60" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18331,10 +18328,10 @@
         <v>1</v>
       </c>
       <c r="N61" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O61" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18374,10 +18371,10 @@
         <v>1</v>
       </c>
       <c r="N62" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O62" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="63" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18417,10 +18414,10 @@
         <v>1</v>
       </c>
       <c r="N63" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O63" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18460,10 +18457,10 @@
         <v>1</v>
       </c>
       <c r="N64" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O64" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18503,10 +18500,10 @@
         <v>1</v>
       </c>
       <c r="N65" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O65" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18546,10 +18543,10 @@
         <v>1</v>
       </c>
       <c r="N66" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O66" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="67" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18589,10 +18586,10 @@
         <v>1</v>
       </c>
       <c r="N67" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O67" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="68" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18632,10 +18629,10 @@
         <v>1</v>
       </c>
       <c r="N68" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O68" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="69" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18675,10 +18672,10 @@
         <v>1</v>
       </c>
       <c r="N69" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O69" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="70" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18718,10 +18715,10 @@
         <v>1</v>
       </c>
       <c r="N70" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O70" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="71" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18761,10 +18758,10 @@
         <v>1</v>
       </c>
       <c r="N71" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="O71" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
   </sheetData>
@@ -18944,10 +18941,10 @@
         <v>1</v>
       </c>
       <c r="L6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="M6" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18983,10 +18980,10 @@
         <v>1</v>
       </c>
       <c r="L7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="M7" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -19022,10 +19019,10 @@
         <v>1</v>
       </c>
       <c r="L8" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="M8" s="12">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -19063,10 +19060,10 @@
         <v>1</v>
       </c>
       <c r="L9" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
       <c r="M9" s="17">
-        <v>46303.70653649306</v>
+        <v>46303.72960831018</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/exports/shuori-demo-workspace.xlsx
+++ b/artifacts/exports/shuori-demo-workspace.xlsx
@@ -89,7 +89,7 @@
     <t>守織 SHUORI · Workbook overview</t>
   </si>
   <si>
-    <t>Generated 2026-10-08 17:31:54 JST · Asia/Tokyo · demo · version 1.3.0</t>
+    <t>Generated 2026-10-08 18:03:47 JST · Asia/Tokyo · demo · version 1.4.0</t>
   </si>
   <si>
     <t>workspace | All records in the stated scope | View label: All saved operational collections</t>
@@ -3017,10 +3017,10 @@
         <v>1</v>
       </c>
       <c r="M6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="N6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3061,10 +3061,10 @@
         <v>1</v>
       </c>
       <c r="M7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="N7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3105,10 +3105,10 @@
         <v>1</v>
       </c>
       <c r="M8" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="N8" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3149,10 +3149,10 @@
         <v>1</v>
       </c>
       <c r="M9" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="N9" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3193,10 +3193,10 @@
         <v>1</v>
       </c>
       <c r="M10" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="N10" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
   </sheetData>
@@ -3903,10 +3903,10 @@
         <v>1</v>
       </c>
       <c r="H6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="I6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3932,10 +3932,10 @@
         <v>1</v>
       </c>
       <c r="H7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="I7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3961,10 +3961,10 @@
         <v>1</v>
       </c>
       <c r="H8" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="I8" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -3990,10 +3990,10 @@
         <v>1</v>
       </c>
       <c r="H9" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="I9" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
   </sheetData>
@@ -4314,10 +4314,10 @@
         <v>1</v>
       </c>
       <c r="Y6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="Z6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
@@ -4388,10 +4388,10 @@
         <v>1</v>
       </c>
       <c r="Y7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="Z7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
@@ -4460,10 +4460,10 @@
         <v>1</v>
       </c>
       <c r="Y8" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="Z8" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
   </sheetData>
@@ -5134,10 +5134,10 @@
         <v>1</v>
       </c>
       <c r="AA6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="AB6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="7" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5208,10 +5208,10 @@
         <v>1</v>
       </c>
       <c r="AA7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="AB7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="8" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5282,10 +5282,10 @@
         <v>1</v>
       </c>
       <c r="AA8" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="AB8" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="9" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5354,10 +5354,10 @@
         <v>1</v>
       </c>
       <c r="AA9" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="AB9" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="10" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5426,10 +5426,10 @@
         <v>1</v>
       </c>
       <c r="AA10" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="AB10" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="11" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5498,10 +5498,10 @@
         <v>1</v>
       </c>
       <c r="AA11" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="AB11" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="12" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5570,10 +5570,10 @@
         <v>1</v>
       </c>
       <c r="AA12" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="AB12" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="13" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5642,10 +5642,10 @@
         <v>1</v>
       </c>
       <c r="AA13" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="AB13" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="14" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5714,10 +5714,10 @@
         <v>1</v>
       </c>
       <c r="AA14" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="AB14" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="15" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5786,10 +5786,10 @@
         <v>1</v>
       </c>
       <c r="AA15" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="AB15" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="16" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5858,10 +5858,10 @@
         <v>1</v>
       </c>
       <c r="AA16" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="AB16" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="17" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -5930,10 +5930,10 @@
         <v>1</v>
       </c>
       <c r="AA17" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="AB17" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="18" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -6002,10 +6002,10 @@
         <v>1</v>
       </c>
       <c r="AA18" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="AB18" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="19" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -6074,10 +6074,10 @@
         <v>1</v>
       </c>
       <c r="AA19" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="AB19" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="20" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -6148,10 +6148,10 @@
         <v>1</v>
       </c>
       <c r="AA20" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="AB20" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="21" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -6222,10 +6222,10 @@
         <v>1</v>
       </c>
       <c r="AA21" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="AB21" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="22" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -6294,10 +6294,10 @@
         <v>1</v>
       </c>
       <c r="AA22" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="AB22" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="23" ht="64" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -6366,10 +6366,10 @@
         <v>1</v>
       </c>
       <c r="AA23" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="AB23" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
   </sheetData>
@@ -6867,10 +6867,10 @@
         <v>1</v>
       </c>
       <c r="N6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -6906,10 +6906,10 @@
         <v>1</v>
       </c>
       <c r="N7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
   </sheetData>
@@ -7547,10 +7547,10 @@
         <v>1</v>
       </c>
       <c r="K6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="L6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7583,10 +7583,10 @@
         <v>1</v>
       </c>
       <c r="K7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="L7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -7619,10 +7619,10 @@
         <v>1</v>
       </c>
       <c r="K8" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="L8" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
   </sheetData>
@@ -7848,10 +7848,10 @@
         <v>1</v>
       </c>
       <c r="P6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="Q6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7901,10 +7901,10 @@
         <v>1</v>
       </c>
       <c r="P7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="Q7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -7954,10 +7954,10 @@
         <v>1</v>
       </c>
       <c r="P8" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="Q8" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -8007,10 +8007,10 @@
         <v>1</v>
       </c>
       <c r="P9" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="Q9" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
   </sheetData>
@@ -8253,10 +8253,10 @@
         <v>1</v>
       </c>
       <c r="R6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="S6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8312,10 +8312,10 @@
         <v>1</v>
       </c>
       <c r="R7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="S7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8371,10 +8371,10 @@
         <v>1</v>
       </c>
       <c r="R8" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="S8" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8430,10 +8430,10 @@
         <v>1</v>
       </c>
       <c r="R9" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="S9" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8489,10 +8489,10 @@
         <v>1</v>
       </c>
       <c r="R10" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="S10" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8548,10 +8548,10 @@
         <v>1</v>
       </c>
       <c r="R11" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="S11" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8603,10 +8603,10 @@
         <v>1</v>
       </c>
       <c r="R12" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="S12" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8662,10 +8662,10 @@
         <v>1</v>
       </c>
       <c r="R13" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="S13" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8721,10 +8721,10 @@
         <v>1</v>
       </c>
       <c r="R14" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="S14" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8780,10 +8780,10 @@
         <v>1</v>
       </c>
       <c r="R15" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="S15" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8835,10 +8835,10 @@
         <v>1</v>
       </c>
       <c r="R16" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="S16" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8890,10 +8890,10 @@
         <v>1</v>
       </c>
       <c r="R17" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="S17" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8949,10 +8949,10 @@
         <v>1</v>
       </c>
       <c r="R18" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="S18" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9008,10 +9008,10 @@
         <v>1</v>
       </c>
       <c r="R19" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="S19" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9063,10 +9063,10 @@
         <v>1</v>
       </c>
       <c r="R20" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="S20" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9122,10 +9122,10 @@
         <v>1</v>
       </c>
       <c r="R21" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="S21" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9181,10 +9181,10 @@
         <v>1</v>
       </c>
       <c r="R22" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="S22" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -9240,10 +9240,10 @@
         <v>1</v>
       </c>
       <c r="R23" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="S23" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
   </sheetData>
@@ -9807,10 +9807,10 @@
         <v>1</v>
       </c>
       <c r="S6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -9869,10 +9869,10 @@
         <v>1</v>
       </c>
       <c r="S7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -9931,10 +9931,10 @@
         <v>1</v>
       </c>
       <c r="S8" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T8" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -9993,10 +9993,10 @@
         <v>1</v>
       </c>
       <c r="S9" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T9" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10055,10 +10055,10 @@
         <v>1</v>
       </c>
       <c r="S10" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T10" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10117,10 +10117,10 @@
         <v>1</v>
       </c>
       <c r="S11" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T11" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10179,10 +10179,10 @@
         <v>1</v>
       </c>
       <c r="S12" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T12" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10241,10 +10241,10 @@
         <v>1</v>
       </c>
       <c r="S13" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T13" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10303,10 +10303,10 @@
         <v>1</v>
       </c>
       <c r="S14" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T14" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10365,10 +10365,10 @@
         <v>1</v>
       </c>
       <c r="S15" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T15" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10427,10 +10427,10 @@
         <v>1</v>
       </c>
       <c r="S16" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T16" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10489,10 +10489,10 @@
         <v>1</v>
       </c>
       <c r="S17" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T17" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10551,10 +10551,10 @@
         <v>1</v>
       </c>
       <c r="S18" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T18" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10613,10 +10613,10 @@
         <v>1</v>
       </c>
       <c r="S19" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T19" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10675,10 +10675,10 @@
         <v>1</v>
       </c>
       <c r="S20" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T20" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10737,10 +10737,10 @@
         <v>1</v>
       </c>
       <c r="S21" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T21" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10799,10 +10799,10 @@
         <v>1</v>
       </c>
       <c r="S22" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T22" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10861,10 +10861,10 @@
         <v>1</v>
       </c>
       <c r="S23" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T23" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10923,10 +10923,10 @@
         <v>1</v>
       </c>
       <c r="S24" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T24" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -10985,10 +10985,10 @@
         <v>1</v>
       </c>
       <c r="S25" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T25" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11047,10 +11047,10 @@
         <v>1</v>
       </c>
       <c r="S26" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T26" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11109,10 +11109,10 @@
         <v>1</v>
       </c>
       <c r="S27" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T27" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11171,10 +11171,10 @@
         <v>1</v>
       </c>
       <c r="S28" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T28" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11233,10 +11233,10 @@
         <v>1</v>
       </c>
       <c r="S29" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T29" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11295,10 +11295,10 @@
         <v>1</v>
       </c>
       <c r="S30" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T30" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11357,10 +11357,10 @@
         <v>1</v>
       </c>
       <c r="S31" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T31" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11419,10 +11419,10 @@
         <v>1</v>
       </c>
       <c r="S32" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T32" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11481,10 +11481,10 @@
         <v>1</v>
       </c>
       <c r="S33" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T33" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11543,10 +11543,10 @@
         <v>1</v>
       </c>
       <c r="S34" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T34" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11605,10 +11605,10 @@
         <v>1</v>
       </c>
       <c r="S35" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T35" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11667,10 +11667,10 @@
         <v>1</v>
       </c>
       <c r="S36" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T36" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11729,10 +11729,10 @@
         <v>1</v>
       </c>
       <c r="S37" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T37" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11791,10 +11791,10 @@
         <v>1</v>
       </c>
       <c r="S38" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T38" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11853,10 +11853,10 @@
         <v>1</v>
       </c>
       <c r="S39" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T39" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11915,10 +11915,10 @@
         <v>1</v>
       </c>
       <c r="S40" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T40" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -11977,10 +11977,10 @@
         <v>1</v>
       </c>
       <c r="S41" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T41" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12039,10 +12039,10 @@
         <v>1</v>
       </c>
       <c r="S42" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T42" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12101,10 +12101,10 @@
         <v>1</v>
       </c>
       <c r="S43" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T43" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12163,10 +12163,10 @@
         <v>1</v>
       </c>
       <c r="S44" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T44" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12225,10 +12225,10 @@
         <v>1</v>
       </c>
       <c r="S45" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T45" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12287,10 +12287,10 @@
         <v>1</v>
       </c>
       <c r="S46" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T46" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12349,10 +12349,10 @@
         <v>1</v>
       </c>
       <c r="S47" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T47" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12411,10 +12411,10 @@
         <v>1</v>
       </c>
       <c r="S48" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T48" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12473,10 +12473,10 @@
         <v>1</v>
       </c>
       <c r="S49" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T49" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12535,10 +12535,10 @@
         <v>1</v>
       </c>
       <c r="S50" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T50" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12597,10 +12597,10 @@
         <v>1</v>
       </c>
       <c r="S51" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T51" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -12659,10 +12659,10 @@
         <v>1</v>
       </c>
       <c r="S52" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="T52" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
   </sheetData>
@@ -15963,10 +15963,10 @@
         <v>1</v>
       </c>
       <c r="N6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16006,10 +16006,10 @@
         <v>1</v>
       </c>
       <c r="N7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16049,10 +16049,10 @@
         <v>1</v>
       </c>
       <c r="N8" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O8" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16092,10 +16092,10 @@
         <v>1</v>
       </c>
       <c r="N9" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O9" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16135,10 +16135,10 @@
         <v>1</v>
       </c>
       <c r="N10" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O10" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16178,10 +16178,10 @@
         <v>1</v>
       </c>
       <c r="N11" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O11" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16221,10 +16221,10 @@
         <v>1</v>
       </c>
       <c r="N12" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O12" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16264,10 +16264,10 @@
         <v>1</v>
       </c>
       <c r="N13" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O13" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16307,10 +16307,10 @@
         <v>1</v>
       </c>
       <c r="N14" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O14" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16350,10 +16350,10 @@
         <v>1</v>
       </c>
       <c r="N15" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O15" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16393,10 +16393,10 @@
         <v>1</v>
       </c>
       <c r="N16" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O16" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16436,10 +16436,10 @@
         <v>1</v>
       </c>
       <c r="N17" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O17" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16479,10 +16479,10 @@
         <v>1</v>
       </c>
       <c r="N18" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O18" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16522,10 +16522,10 @@
         <v>1</v>
       </c>
       <c r="N19" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O19" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16565,10 +16565,10 @@
         <v>1</v>
       </c>
       <c r="N20" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O20" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16608,10 +16608,10 @@
         <v>1</v>
       </c>
       <c r="N21" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O21" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16651,10 +16651,10 @@
         <v>1</v>
       </c>
       <c r="N22" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O22" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16694,10 +16694,10 @@
         <v>1</v>
       </c>
       <c r="N23" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O23" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16737,10 +16737,10 @@
         <v>1</v>
       </c>
       <c r="N24" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O24" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16780,10 +16780,10 @@
         <v>1</v>
       </c>
       <c r="N25" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O25" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16823,10 +16823,10 @@
         <v>1</v>
       </c>
       <c r="N26" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O26" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16866,10 +16866,10 @@
         <v>1</v>
       </c>
       <c r="N27" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O27" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16909,10 +16909,10 @@
         <v>1</v>
       </c>
       <c r="N28" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O28" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="29" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16952,10 +16952,10 @@
         <v>1</v>
       </c>
       <c r="N29" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O29" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16995,10 +16995,10 @@
         <v>1</v>
       </c>
       <c r="N30" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O30" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17038,10 +17038,10 @@
         <v>1</v>
       </c>
       <c r="N31" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O31" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17081,10 +17081,10 @@
         <v>1</v>
       </c>
       <c r="N32" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O32" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17124,10 +17124,10 @@
         <v>1</v>
       </c>
       <c r="N33" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O33" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17167,10 +17167,10 @@
         <v>1</v>
       </c>
       <c r="N34" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O34" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17210,10 +17210,10 @@
         <v>1</v>
       </c>
       <c r="N35" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O35" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17253,10 +17253,10 @@
         <v>1</v>
       </c>
       <c r="N36" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O36" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17296,10 +17296,10 @@
         <v>1</v>
       </c>
       <c r="N37" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O37" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17339,10 +17339,10 @@
         <v>1</v>
       </c>
       <c r="N38" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O38" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17382,10 +17382,10 @@
         <v>1</v>
       </c>
       <c r="N39" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O39" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17425,10 +17425,10 @@
         <v>1</v>
       </c>
       <c r="N40" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O40" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17468,10 +17468,10 @@
         <v>1</v>
       </c>
       <c r="N41" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O41" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17511,10 +17511,10 @@
         <v>1</v>
       </c>
       <c r="N42" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O42" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="43" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17554,10 +17554,10 @@
         <v>1</v>
       </c>
       <c r="N43" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O43" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17597,10 +17597,10 @@
         <v>1</v>
       </c>
       <c r="N44" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O44" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17640,10 +17640,10 @@
         <v>1</v>
       </c>
       <c r="N45" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O45" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17683,10 +17683,10 @@
         <v>1</v>
       </c>
       <c r="N46" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O46" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17726,10 +17726,10 @@
         <v>1</v>
       </c>
       <c r="N47" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O47" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17769,10 +17769,10 @@
         <v>1</v>
       </c>
       <c r="N48" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O48" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17812,10 +17812,10 @@
         <v>1</v>
       </c>
       <c r="N49" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O49" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17855,10 +17855,10 @@
         <v>1</v>
       </c>
       <c r="N50" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O50" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17898,10 +17898,10 @@
         <v>1</v>
       </c>
       <c r="N51" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O51" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="52" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17941,10 +17941,10 @@
         <v>1</v>
       </c>
       <c r="N52" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O52" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="53" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -17984,10 +17984,10 @@
         <v>1</v>
       </c>
       <c r="N53" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O53" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18027,10 +18027,10 @@
         <v>1</v>
       </c>
       <c r="N54" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O54" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18070,10 +18070,10 @@
         <v>1</v>
       </c>
       <c r="N55" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O55" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18113,10 +18113,10 @@
         <v>1</v>
       </c>
       <c r="N56" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O56" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="57" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18156,10 +18156,10 @@
         <v>1</v>
       </c>
       <c r="N57" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O57" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="58" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18199,10 +18199,10 @@
         <v>1</v>
       </c>
       <c r="N58" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O58" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="59" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18242,10 +18242,10 @@
         <v>1</v>
       </c>
       <c r="N59" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O59" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="60" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18285,10 +18285,10 @@
         <v>1</v>
       </c>
       <c r="N60" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O60" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="61" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18328,10 +18328,10 @@
         <v>1</v>
       </c>
       <c r="N61" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O61" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="62" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18371,10 +18371,10 @@
         <v>1</v>
       </c>
       <c r="N62" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O62" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="63" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18414,10 +18414,10 @@
         <v>1</v>
       </c>
       <c r="N63" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O63" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18457,10 +18457,10 @@
         <v>1</v>
       </c>
       <c r="N64" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O64" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18500,10 +18500,10 @@
         <v>1</v>
       </c>
       <c r="N65" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O65" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18543,10 +18543,10 @@
         <v>1</v>
       </c>
       <c r="N66" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O66" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="67" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18586,10 +18586,10 @@
         <v>1</v>
       </c>
       <c r="N67" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O67" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="68" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18629,10 +18629,10 @@
         <v>1</v>
       </c>
       <c r="N68" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O68" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="69" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18672,10 +18672,10 @@
         <v>1</v>
       </c>
       <c r="N69" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O69" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="70" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18715,10 +18715,10 @@
         <v>1</v>
       </c>
       <c r="N70" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O70" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="71" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -18758,10 +18758,10 @@
         <v>1</v>
       </c>
       <c r="N71" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="O71" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
   </sheetData>
@@ -18941,10 +18941,10 @@
         <v>1</v>
       </c>
       <c r="L6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="M6" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -18980,10 +18980,10 @@
         <v>1</v>
       </c>
       <c r="L7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="M7" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -19019,10 +19019,10 @@
         <v>1</v>
       </c>
       <c r="L8" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="M8" s="12">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -19060,10 +19060,10 @@
         <v>1</v>
       </c>
       <c r="L9" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
       <c r="M9" s="17">
-        <v>46303.72960831018</v>
+        <v>46303.745052638886</v>
       </c>
     </row>
   </sheetData>
